--- a/workshop_registration_form_templates/004_sustainability_forum_panelist_registration_form--workshop_registration_form_templates.xlsx
+++ b/workshop_registration_form_templates/004_sustainability_forum_panelist_registration_form--workshop_registration_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -692,8 +692,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -721,12 +721,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'carbon_footprint_reduction'}</t>
+          <t>carbon_footprint_reduction</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Carbon Footprint Reduction'}</t>
+          <t>Carbon Footprint Reduction</t>
         </is>
       </c>
     </row>
@@ -738,12 +738,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'supply_chain_optimization'}</t>
+          <t>supply_chain_optimization</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Supply Chain Optimization'}</t>
+          <t>Supply Chain Optimization</t>
         </is>
       </c>
     </row>
@@ -755,12 +755,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'sustainable_materials'}</t>
+          <t>sustainable_materials</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Sustainable Materials'}</t>
+          <t>Sustainable Materials</t>
         </is>
       </c>
     </row>
@@ -772,12 +772,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'waste_minimization'}</t>
+          <t>waste_minimization</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Waste Minimization'}</t>
+          <t>Waste Minimization</t>
         </is>
       </c>
     </row>
@@ -789,12 +789,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'energy_conservation'}</t>
+          <t>energy_conservation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Energy Conservation'}</t>
+          <t>Energy Conservation</t>
         </is>
       </c>
     </row>
@@ -806,12 +806,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'water_management'}</t>
+          <t>water_management</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Water Management'}</t>
+          <t>Water Management</t>
         </is>
       </c>
     </row>
